--- a/docs/downloads/04/tbl_other_act_sex_alaotra_ambodivoara.xlsx
+++ b/docs/downloads/04/tbl_other_act_sex_alaotra_ambodivoara.xlsx
@@ -512,12 +512,6 @@
           <t>Étudiant</t>
         </is>
       </c>
-      <c r="D7">
-        <v>4</v>
-      </c>
-      <c r="E7">
-        <v>4.1</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -558,12 +552,6 @@
           <t>Chômeur</t>
         </is>
       </c>
-      <c r="D9">
-        <v>3</v>
-      </c>
-      <c r="E9">
-        <v>4.4</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -604,12 +592,6 @@
           <t>Ouvrier agricole</t>
         </is>
       </c>
-      <c r="D11">
-        <v>3</v>
-      </c>
-      <c r="E11">
-        <v>4.4</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -627,12 +609,6 @@
           <t>Étudiant</t>
         </is>
       </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -765,12 +741,6 @@
           <t>Pêcheur exploitant</t>
         </is>
       </c>
-      <c r="D18">
-        <v>3</v>
-      </c>
-      <c r="E18">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -880,12 +850,6 @@
           <t>Commerçant</t>
         </is>
       </c>
-      <c r="D23">
-        <v>2</v>
-      </c>
-      <c r="E23">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -948,12 +912,6 @@
         <is>
           <t>Éleveur</t>
         </is>
-      </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-      <c r="E26">
-        <v>0.2</v>
       </c>
     </row>
     <row r="27">

--- a/docs/downloads/04/tbl_other_act_sex_alaotra_ambodivoara.xlsx
+++ b/docs/downloads/04/tbl_other_act_sex_alaotra_ambodivoara.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -394,14 +394,8 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D2">
-        <v>44</v>
-      </c>
-      <c r="E2">
-        <v>44.9</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -417,14 +411,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>5.1</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="4">
@@ -440,14 +434,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>10.2</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="5">
@@ -463,14 +457,8 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>28</v>
-      </c>
-      <c r="E5">
-        <v>28.6</v>
+          <t>Elève / Etudiant</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -493,7 +481,7 @@
         <v>7</v>
       </c>
       <c r="E6">
-        <v>7.1</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="7">
@@ -509,8 +497,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Étudiant</t>
-        </is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>13.1</v>
       </c>
     </row>
     <row r="8">
@@ -526,14 +520,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D8">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="E8">
-        <v>67.59999999999999</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="9">
@@ -549,7 +543,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
     </row>
@@ -566,14 +560,8 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>15</v>
-      </c>
-      <c r="E10">
-        <v>22.1</v>
+          <t>Elève / Etudiant</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -606,8 +594,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Étudiant</t>
-        </is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>6</v>
+      </c>
+      <c r="E12">
+        <v>21.4</v>
       </c>
     </row>
     <row r="13">
@@ -623,14 +617,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="D13">
-        <v>405</v>
+        <v>18</v>
       </c>
       <c r="E13">
-        <v>46.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="14">
@@ -646,14 +640,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D14">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="E14">
-        <v>3.1</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="15">
@@ -669,14 +663,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D15">
-        <v>62</v>
+        <v>289</v>
       </c>
       <c r="E15">
-        <v>7.1</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="16">
@@ -692,14 +686,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="D16">
-        <v>289</v>
+        <v>19</v>
       </c>
       <c r="E16">
-        <v>33</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="17">
@@ -715,14 +709,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D17">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="E17">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="18">
@@ -738,8 +732,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pêcheur exploitant</t>
-        </is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>57</v>
+      </c>
+      <c r="E18">
+        <v>10.8</v>
       </c>
     </row>
     <row r="19">
@@ -755,14 +755,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D19">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="E19">
-        <v>0.9</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -773,19 +773,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="D20">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="21">
@@ -801,14 +801,8 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>418</v>
-      </c>
-      <c r="E21">
-        <v>71.5</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -824,14 +818,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D22">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="E22">
-        <v>3.2</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="23">
@@ -847,8 +841,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>16</v>
+      </c>
+      <c r="E23">
+        <v>7.5</v>
       </c>
     </row>
     <row r="24">
@@ -864,14 +864,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D24">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="E24">
-        <v>17.3</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="25">
@@ -894,7 +894,7 @@
         <v>19</v>
       </c>
       <c r="E25">
-        <v>3.2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
@@ -910,31 +910,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Étudiant</t>
-        </is>
-      </c>
-      <c r="D27">
-        <v>25</v>
-      </c>
-      <c r="E27">
-        <v>4.3</v>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>38</v>
+      </c>
+      <c r="E26">
+        <v>17.9</v>
       </c>
     </row>
   </sheetData>
